--- a/Data/EXCEL/Transfer/salemon/202208/8941-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8941-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8A17443-5A40-4B9E-BB04-455880463909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1891758-F0A2-457C-8F20-53AD2D64BFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8941-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,21 +1227,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q264"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="13" width="8.625" customWidth="1"/>
-    <col min="14" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1266,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1299,7 +1305,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1342,7 +1348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1381,7 +1387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1487,7 +1493,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1540,7 +1546,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1593,7 +1599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1646,7 +1652,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1699,7 +1705,7 @@
         <v>31.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1752,7 +1758,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1858,7 +1864,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1911,7 +1917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1964,7 +1970,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2017,7 +2023,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2070,7 +2076,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2176,7 +2182,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2229,7 +2235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2282,7 +2288,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2335,7 +2341,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2388,7 +2394,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2441,7 +2447,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2494,7 +2500,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2547,7 +2553,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2600,7 +2606,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2653,7 +2659,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2706,7 +2712,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2759,7 +2765,7 @@
         <v>-0.55000000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2812,7 +2818,7 @@
         <v>-0.77</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2865,7 +2871,7 @@
         <v>-2.82</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2918,7 +2924,7 @@
         <v>-7.96</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2971,7 +2977,7 @@
         <v>-3.49</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3024,7 +3030,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3077,7 +3083,7 @@
         <v>-9.6</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3130,7 +3136,7 @@
         <v>-3.85</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>-3.81</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3236,7 +3242,7 @@
         <v>-2.5499999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3289,7 +3295,7 @@
         <v>-2.69</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3342,7 +3348,7 @@
         <v>-1.05</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3395,7 +3401,7 @@
         <v>-0.92</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3448,7 +3454,7 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3501,7 +3507,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3554,7 +3560,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3607,7 +3613,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3660,7 +3666,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3713,7 +3719,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3819,7 +3825,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3872,7 +3878,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3925,7 +3931,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3978,7 +3984,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4031,7 +4037,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4084,7 +4090,7 @@
         <v>-1.41</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4137,7 +4143,7 @@
         <v>-5.84</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4190,7 +4196,7 @@
         <v>-6.65</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4243,7 +4249,7 @@
         <v>-9.02</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4296,7 +4302,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4349,7 +4355,7 @@
         <v>-18.2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4402,7 +4408,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4455,7 +4461,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4508,7 +4514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4561,7 +4567,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4614,7 +4620,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4667,7 +4673,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4720,7 +4726,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4773,7 +4779,7 @@
         <v>-1.41</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4826,7 +4832,7 @@
         <v>-3.87</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4879,7 +4885,7 @@
         <v>-6.17</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4932,7 +4938,7 @@
         <v>-9.43</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4985,7 +4991,7 @@
         <v>-8.65</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5038,7 +5044,7 @@
         <v>-2.3199999999999998</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5091,7 +5097,7 @@
         <v>-1.63</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5144,7 +5150,7 @@
         <v>-0.79</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5197,7 +5203,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5250,7 +5256,7 @@
         <v>-0.65</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5303,7 +5309,7 @@
         <v>-1.79</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5356,7 +5362,7 @@
         <v>-2.5099999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5409,7 +5415,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5462,7 +5468,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5515,7 +5521,7 @@
         <v>-0.81</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5568,7 +5574,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5621,7 +5627,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5674,7 +5680,7 @@
         <v>-0.63</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5727,7 +5733,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5780,7 +5786,7 @@
         <v>-3.15</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5833,7 +5839,7 @@
         <v>-3.35</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5886,7 +5892,7 @@
         <v>-2.06</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5939,7 +5945,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5992,7 +5998,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6045,7 +6051,7 @@
         <v>-0.99</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6098,7 +6104,7 @@
         <v>-3.78</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6151,7 +6157,7 @@
         <v>-5.18</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6204,7 +6210,7 @@
         <v>-7.79</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6257,7 +6263,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6310,7 +6316,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6363,7 +6369,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6416,7 +6422,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6469,7 +6475,7 @@
         <v>-11.7</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6522,7 +6528,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6575,7 +6581,7 @@
         <v>-17.600000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6628,7 +6634,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6681,7 +6687,7 @@
         <v>-21.2</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6734,7 +6740,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6787,7 +6793,7 @@
         <v>-20.7</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6840,7 +6846,7 @@
         <v>-19.600000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6893,7 +6899,7 @@
         <v>-27.4</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6946,7 +6952,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6999,7 +7005,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7052,7 +7058,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7105,7 +7111,7 @@
         <v>-17.600000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7158,7 +7164,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7211,7 +7217,7 @@
         <v>-17.399999999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7264,7 +7270,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7317,7 +7323,7 @@
         <v>-16.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7370,7 +7376,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7423,7 +7429,7 @@
         <v>-20.3</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7476,7 +7482,7 @@
         <v>-21.4</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>-19.100000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7582,7 +7588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7635,7 +7641,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7688,7 +7694,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7741,7 +7747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7794,7 +7800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7847,7 +7853,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7900,7 +7906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7953,7 +7959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8006,7 +8012,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8059,7 +8065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8112,7 +8118,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8165,7 +8171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8218,7 +8224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8271,7 +8277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8324,7 +8330,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8377,7 +8383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8430,7 +8436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8483,7 +8489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8536,7 +8542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8589,7 +8595,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8642,7 +8648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8695,7 +8701,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8748,7 +8754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8801,7 +8807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8854,7 +8860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8907,7 +8913,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8960,7 +8966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9013,7 +9019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9066,7 +9072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9119,7 +9125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9172,7 +9178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9225,7 +9231,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9278,7 +9284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9331,7 +9337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9384,7 +9390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9437,7 +9443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9490,7 +9496,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9543,7 +9549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9596,7 +9602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9649,7 +9655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9702,7 +9708,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9755,7 +9761,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9808,7 +9814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9861,7 +9867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9914,7 +9920,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9967,7 +9973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10020,7 +10026,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10073,7 +10079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10126,7 +10132,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10179,7 +10185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10232,7 +10238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10285,7 +10291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10338,7 +10344,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10391,7 +10397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10444,7 +10450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10497,7 +10503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10550,7 +10556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10603,7 +10609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10656,7 +10662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10709,7 +10715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10762,7 +10768,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10815,7 +10821,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10868,7 +10874,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10921,7 +10927,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10974,7 +10980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11027,7 +11033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11080,7 +11086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11133,7 +11139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11186,7 +11192,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11239,7 +11245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11292,7 +11298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11345,7 +11351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11398,7 +11404,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11451,7 +11457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11504,7 +11510,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11557,7 +11563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11610,7 +11616,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11663,7 +11669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11716,7 +11722,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11769,7 +11775,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11822,7 +11828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11875,7 +11881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11928,7 +11934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11981,7 +11987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12034,7 +12040,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12087,7 +12093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12140,7 +12146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12193,7 +12199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12246,7 +12252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12299,7 +12305,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12352,7 +12358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12405,7 +12411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12458,7 +12464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12511,7 +12517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12564,7 +12570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12617,7 +12623,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12670,7 +12676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12723,7 +12729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12776,7 +12782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12829,7 +12835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12882,7 +12888,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12935,7 +12941,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12988,7 +12994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13041,7 +13047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13094,7 +13100,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13147,7 +13153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13200,7 +13206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13253,7 +13259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13306,7 +13312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13359,7 +13365,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13412,7 +13418,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13465,7 +13471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13518,7 +13524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13571,7 +13577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13624,7 +13630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13677,7 +13683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13730,7 +13736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13783,7 +13789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13836,7 +13842,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13889,7 +13895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" s="5" customFormat="1">
+    <row r="241" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>37591</v>
       </c>
@@ -13942,7 +13948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" s="5" customFormat="1">
+    <row r="242" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>37561</v>
       </c>
@@ -13995,7 +14001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" s="5" customFormat="1">
+    <row r="243" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>37530</v>
       </c>
@@ -14048,7 +14054,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" s="5" customFormat="1">
+    <row r="244" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>37500</v>
       </c>
@@ -14101,7 +14107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" s="5" customFormat="1">
+    <row r="245" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>37469</v>
       </c>
@@ -14154,7 +14160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" s="5" customFormat="1">
+    <row r="246" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>37438</v>
       </c>
@@ -14207,7 +14213,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" s="5" customFormat="1">
+    <row r="247" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>37408</v>
       </c>
@@ -14260,7 +14266,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" s="5" customFormat="1">
+    <row r="248" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>37377</v>
       </c>
@@ -14313,7 +14319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1">
+    <row r="249" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>37347</v>
       </c>
@@ -14366,7 +14372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1">
+    <row r="250" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>37316</v>
       </c>
@@ -14419,7 +14425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1">
+    <row r="251" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>37288</v>
       </c>
@@ -14472,7 +14478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1">
+    <row r="252" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>37257</v>
       </c>
@@ -14525,7 +14531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:17" s="5" customFormat="1">
+    <row r="253" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>37226</v>
       </c>
@@ -14578,7 +14584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:17" s="5" customFormat="1">
+    <row r="254" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>37196</v>
       </c>
@@ -14631,7 +14637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:17" s="5" customFormat="1">
+    <row r="255" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>37165</v>
       </c>
@@ -14684,7 +14690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:17" s="5" customFormat="1">
+    <row r="256" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>37135</v>
       </c>
@@ -14737,7 +14743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:17" s="5" customFormat="1">
+    <row r="257" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>37104</v>
       </c>
@@ -14790,7 +14796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:17" s="5" customFormat="1">
+    <row r="258" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>37073</v>
       </c>
@@ -14843,7 +14849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:17" s="5" customFormat="1">
+    <row r="259" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>37043</v>
       </c>
@@ -14896,7 +14902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="260" spans="1:17" s="5" customFormat="1">
+    <row r="260" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>37012</v>
       </c>
@@ -14949,7 +14955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:17" s="5" customFormat="1">
+    <row r="261" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>36982</v>
       </c>
@@ -15002,7 +15008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:17" s="5" customFormat="1">
+    <row r="262" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>36951</v>
       </c>
@@ -15055,7 +15061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:17" s="5" customFormat="1">
+    <row r="263" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>36923</v>
       </c>
@@ -15108,7 +15114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:17" s="5" customFormat="1">
+    <row r="264" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>36892</v>
       </c>
@@ -15176,7 +15182,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>